--- a/Result/checksun_type/工業用設備.xlsx
+++ b/Result/checksun_type/工業用設備.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>251.2</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>258.15</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>260.34</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>258.15</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>260.34</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>62122.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>91503.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>91503.60000000001</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>95122.9</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>231552.36</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>231552.36</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-21661.49985951927</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>62122</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>62122.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>247.8</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>259.1</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>260.86</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>259.1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>260.86</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>38307.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>91500.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>91500.39999999999</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>123933.6</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>255976.44</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>255976.44</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-21118.31036702263</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>38307</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>38307.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>245.5</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>259.95</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>261.42</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>259.95</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>261.42</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>90026.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>106275.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>106275.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>135094.9</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>259308.18</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>259308.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-17036.49286463374</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>90026</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>90026.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>245.0</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>261.3</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>262.08</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>261.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>262.08</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>139398.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>107196.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>107196</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>134680.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>264270.1</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>264270.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-16138.20025891271</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>139398</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>139398.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>244.2</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>262.5</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>262.77</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>262.77</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>127665.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>106467.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>106467.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>134710.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>272115.22</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>272115.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-19568.41795577864</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>127665</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>127665.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>243.7</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>263.58</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>263.27</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>263.58</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>263.27</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>62106.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>98742.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>98742.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>131005.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>275852.94</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>275852.94</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-22512.74973859498</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>62106</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>62106.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>247.1</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>265.48</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>264.0</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>265.48</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>264</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>112184.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>156366.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>156366.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>136726.2</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>286677.98</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>286677.98</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-18890.73265195425</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>112184</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>112184.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>252.9</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>267.23</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>264.93</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>267.23</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>264.93</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>94627.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>163914.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>163914</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>147017.4</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>301340.44</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>301340.44</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-18407.2535048977</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>94627</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>94627.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>257.2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>268.9</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>265.72</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>268.9</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>265.72</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>135755.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>162165.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>162165.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>158536.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>327478.82</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>327478.82</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-15178.05995535626</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>135755</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>135755.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>260.7</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>270.75</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>266.28</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>270.75</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>266.28</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>89039.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>162953.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>162953.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>168609.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>360844.1</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>360844.1</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-14429.4241718915</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>89039</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>89039.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>263.7</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>272.05</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>266.43</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>272.05</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>266.43</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>350229.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>163267.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>163267.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>174802.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>374295.42</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>374295.42</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-7839.322189374274</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>350229</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>350229.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>80.32000000000001</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>83.28</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>83.76</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>83.28</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>83.76000000000001</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>6154.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>11416.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>11416</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>14200.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>19092.5</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>19092.5</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-2276.381225536164</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>6154</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>6154.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>79.82</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>83.32</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>83.95</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>83.31999999999999</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>83.95</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>7843.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>13837.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>13837.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>17431.8</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>19372.7</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>19372.7</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-1847.58152362209</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>7843</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>7843.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>79.88</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>83.48</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>84.18</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>83.48</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>84.18000000000001</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>9429.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>17352.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>17352.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>19005.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>19449.8</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>19449.8</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-1349.98975218691</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>9429</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>9429.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>80.98</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>83.71</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>84.41</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>83.70999999999999</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>84.41</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>12303.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>17354.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>17354</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>19326.6</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>19488.74</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>19488.74</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-760.8590161299762</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>12303</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>12303.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>81.96000000000001</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>84.68</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>84</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>84.68000000000001</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>21351.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>17917.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>17917.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>19846.7</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>19569.2</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>19569.2</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-199.9987140439989</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>21351</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>21351.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>82.96000000000001</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>84.3</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>84.92</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>84.92</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>18262.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>16985.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>16985.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>20408.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>19515.22</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>19515.22</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-361.055471276748</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>18262</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>18262.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>84.48</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>84.84</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>85.2</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>84.84</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>85.2</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>25418.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>21026.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>21026</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>22200.4</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>20361.92</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>20361.92</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-247.277429063648</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>25418</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>25418.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>85.7</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>85.18</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>85.47</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>85.18000000000001</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>85.47</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>9436.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>20658.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>20658.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>22253.0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>20413.76</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>20413.76</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-842.6203177212301</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>9436</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>9436.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>85.22</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>85.06</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>85.63</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>85.06</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>85.63</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>15121.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>21299.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>21299.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>23448.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>21080.66</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>21080.66</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>49.34056697226697</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>15121</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>15121.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>85.38</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>85.1</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>85.8</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>85.8</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>16690.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>21775.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>21775.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>23259.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>21155.18</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>21155.18</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>712.7010962853965</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>16690</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>16690.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>85.42</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>84.87</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>85.95</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>84.87</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>85.95</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>38465.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>23831.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>23831</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>22246.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>21400.92</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>21400.92</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>1466.798241865392</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>38465</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>38465.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>27.17</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>28.29</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>30.77</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>30.77</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>3050.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>4567.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>4567</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>6476.6</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>33485.9</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>33485.9</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-2146.382417094681</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>3050</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>3050.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>27.09</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>28.45</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>30.91</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>30.91</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>4410.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>5096.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>5096.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>6745.2</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>35229.26</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>35229.26</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-2155.818147479023</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>4410</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>4410.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>27.09</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>28.65</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>31.08</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>31.08</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>3637.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>6183.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>6183.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>7060.0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>38953.24</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>38953.24</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-2238.018542760976</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>3637</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>3637.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>27.08</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>28.87</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>31.2</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>31.2</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>7439.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>7350.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>7350.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>7674.1</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>41416.7</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>41416.7</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-2192.697016636587</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>7439</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>7439.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>27.3</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>29.14</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>31.36</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>31.36</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>4299.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>7206.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>7206.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>8562.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>44696.44</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>44696.44</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-2456.998514436155</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>4299</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>4299.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>27.43</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>29.38</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>31.48</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>31.48</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>5697.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>8386.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>8386.200000000001</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>9223.8</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>49893.98</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>49893.98</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-2410.393564348531</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>5697</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>5697.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>27.7</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>29.6</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>31.57</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>31.57</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>9846.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>8394.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>8394</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>10008.8</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>54470.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>54470</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-2407.515294068049</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>9846</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>9846.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>27.89</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>29.79</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>31.61</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>29.79</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>31.61</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>9470.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>7936.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>7936.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>9804.3</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>56750.64</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>56750.64</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-2761.956504593501</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>9470</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>9470.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>28.08</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>29.95</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>31.62</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>31.62</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>6721.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>7998.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>7998</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>9665.3</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>57098.14</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>57098.14</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-3129.374073037236</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>6721</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>6721.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>28.27</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>30.1</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>31.61</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>31.61</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>10197.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>9919.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>9919.200000000001</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>10047.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>57347.1</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>57347.1</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-3247.957239634103</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>10197</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>10197.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>28.64</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>30.22</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>31.59</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>30.22</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>31.59</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>5736.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>10061.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>10061.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>11059.2</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>57452.02</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>57452.02</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-3673.791861928406</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>5736</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>5736.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>70.2</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>73.05</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>69.14</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>73.05</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>69.14</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>33572.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>33291.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>33291.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>79907.5</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>52563.6</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>52563.6</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-8451.833814836384</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>33572</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>33572.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>69.84</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>73.08</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>68.96</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>73.08</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>68.95999999999999</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>23968.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>35206.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>35206.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>78572.9</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>52193.48</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>52193.48</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-7285.714174139335</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>23968</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>23968.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>69.86</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>73.16</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>68.81</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>73.16</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>68.81</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>18778.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>49174.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>49174.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>80723.8</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>51860.5</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>51860.5</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-4330.624895495712</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>18778</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>18778.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>71.06</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>73.26</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>68.69</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>73.26000000000001</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>68.69</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>41249.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>126334.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>126334.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>84751.5</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>51658.1</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>51658.1</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>601.6678202628682</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>41249</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>41249.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>72.34</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>73.44</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>68.61</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>68.61</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>48891.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>126537.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>126537</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>90533.7</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>50941.56</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>50941.56</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>5218.704992051455</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>48891</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>48891.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>72.91999999999999</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>73.49</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>68.47</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>73.48999999999999</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>68.47</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>43146.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>126523.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>126523.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>110266.6</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>50056.24</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>50056.24</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>10809.30434489046</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>43146</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>43146.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>73.17999999999999</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>73.4</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>68.33</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>68.33</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>93810.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>121939.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>121939.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>111374.5</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>49406.96</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>49406.96</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>19025.36397948582</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>93810</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>93810.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>73.62</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>73.16</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>68.19</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>73.16</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>68.19</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>404577.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>112272.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>112272.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>106038.9</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>47927.76</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>47927.76</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>24654.82902964039</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>404577</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>404577.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>73.38000000000001</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>72.71</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>72.70999999999999</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>68</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>42261.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>43168.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>43168.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>71541.8</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>40084.32</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>40084.32</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-1480.071935483087</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>42261</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>42261.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>73.2</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>72.32</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>67.81</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>72.31999999999999</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>67.81</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>48823.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>54530.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>54530.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>71688.6</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>39731.78</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>39731.78</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>56.78639775064221</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>48823</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>48823.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>72.96</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>71.85</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>67.68</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>67.68000000000001</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>20226.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>94009.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>94009.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>77244.4</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>38919.48</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>38919.48</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>1547.198788164882</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>20226</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>20226.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>50.48</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>54.81</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>59.08</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>59.08</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>2123.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>1895.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>1895.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>2811.5</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>5367.5</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>5367.5</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-720.1064270368502</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>2123</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>2123.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>50.45</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>55.36</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>59.33</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>55.36</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>59.33</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>2214.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>1713.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>1713.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>3734.4</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>5569.18</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>5569.18</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-748.2164055027056</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>2214</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>2214.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>50.19</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>55.89</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>59.61</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>55.89</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>59.61</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>965.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>2228.6</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>2228.6</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>4310.9</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>5835.32</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>5835.32</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-771.4015031145454</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>965</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>965.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>50.55</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>56.49</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>59.96</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>59.96</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>1489.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>3649.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>3649.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>4762.5</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>6143.92</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>6143.92</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-643.1515888773692</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>1489</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>1489.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>51.39000000000001</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>57.11</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>60.34</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>60.34</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>2688.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>3814.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>3814.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>4797.5</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>6562.3</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>6562.3</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-493.1105832214971</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>2688</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>2688.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>52.37</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>57.68</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>60.64</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>60.64</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>1211.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>3727.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>3727.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>5191.4</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>7081.28</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>7081.28</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-389.6194828837688</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1211</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1211.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>53.67999999999999</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>58.37</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>60.95</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>60.95</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>4790.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>5755.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>5755.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>5737.1</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>7281.4</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>7281.4</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-69.61007229830739</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>4790</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>4790.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>54.86</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>59.06</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>61.28</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>59.06</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>61.28</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>8069.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>6393.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>6393.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>6276.8</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>7542.9</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>7542.9</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>6.568016834434275</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>8069</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>8069.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>56.06</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>59.64</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>61.6</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>59.64</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>61.6</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>2313.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>5875.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>5875.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>5978.1</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>9177.78</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>9177.780000000001</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-236.1621421485943</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>2313</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>2313.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>56.58</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>60.08</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>61.85</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>60.08</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>61.85</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>2253.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>5780.8</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>5780.8</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>5923.4</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>9749.82</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>9749.82</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>42.229135809529</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>2253</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>2253.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>57.04</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>60.43</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>61.96</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>60.43</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>61.96</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>11352.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>6655.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>6655.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>6076.3</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>9802.68</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>9802.68</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>444.851349470794</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>11352</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>11352.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>153.9</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>160.25</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>164.17</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>160.25</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>164.17</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>70051.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>56058.2</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>56058.2</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>72932.1</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>207945.5</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>207945.5</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-26589.48995717692</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>70051</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>70051.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>152.3</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>161.18</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>164.34</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>161.18</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>164.34</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>35314.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>57863.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>57863.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>75490.5</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>210633.34</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>210633.34</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-29998.31826927271</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>35314</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>35314.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>151.9</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>162.1</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>164.66</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>162.1</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>164.66</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>27273.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>73678.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>73678.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>96638.5</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>211870.9</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>211870.9</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-30074.88306264984</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>27273</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>27273.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>152.2</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>163.25</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>165.01</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>163.25</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>165.01</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>70357.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>85025.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>85025</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>103195.3</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>214487.18</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>214487.18</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-28248.62265809395</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>70357</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>70357.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>154.0</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>164.4</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>165.5</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>165.5</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>77296.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>83838.8</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>83838.8</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>107411.9</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>218227.42</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>218227.42</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-29246.94269951076</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>77296</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>77296.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>155.0</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>165.48</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>165.7</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>165.48</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>165.7</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>79077.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>89806.0</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>89806</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>105606.8</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>218804.58</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>218804.58</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-30372.04480512367</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>79077</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>79077.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>157.9</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>166.8</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>166.04</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>166.8</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>166.04</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>114388.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>93117.6</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>93117.60000000001</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>108574.1</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>222110.76</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>222110.76</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-31085.43907010197</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>114388</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>114388.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>159.9</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>167.9</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>166.34</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>166.34</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>84007.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>119598.8</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>119598.8</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>124302.4</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>221679.1</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>221679.1</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-34777.70091042449</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>84007</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>84007.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>161.4</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>168.95</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>166.61</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>168.95</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>166.61</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>64426.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>121365.6</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>121365.6</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>130208.0</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>223777.34</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>223777.34</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-35555.19279265575</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>64426</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>64426.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>161.9</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>169.98</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>166.86</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>169.98</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>166.86</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>107132.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>130985.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>130985</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>141476.5</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>228728.42</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>228728.42</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-33298.10288181988</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>107132</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>107132.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>163.0</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>171.1</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>167.17</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>171.1</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>167.17</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>95635.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>121407.6</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>121407.6</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>152961.2</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>232438.7</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>232438.7</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-33460.11362056076</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>95635</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>95635.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>49.16</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>47.79</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>48.09</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>47.79</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>48.09</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>58151.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>33826.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>33826</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>31804.6</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>30566.2</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>30566.2</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>1847.910848564396</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>58151</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>58151.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>47.98</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>48.04</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>48.04</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>38893.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>25373.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>25373.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>41099.0</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>32485.34</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>32485.34</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-162.6197830090241</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>38893</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>38893.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>47.09</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>47.39</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>47.39</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>48.1</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>31012.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>22443.4</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>22443.4</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>45329.6</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>48091.44</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>48091.44</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-965.6414072921507</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>31012</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>31012.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,21 +30727,17 @@
           <t>46.95</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>47.31</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
+      <c r="AM71" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="AO71" t="inlineStr">
         <is>
           <t>48.22</t>
         </is>
       </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>48.22</t>
-        </is>
-      </c>
       <c r="AP71" t="inlineStr">
         <is>
           <t>-2163.74</t>
@@ -31196,20 +30778,16 @@
           <t>18517.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>22345.0</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>22345</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>43701.5</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>52580.36</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>52580.36</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-1233.935106007615</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>18517</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>18517.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>47.69</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>48.29</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>48.29</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>22557.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>22850.4</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>22850.4</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>42672.1</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>52972.04</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>52972.04</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-234.3927075294341</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>22557</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>22557.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>48.33</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>48.3</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>48.3</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>15888.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>29783.2</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>29783.2</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>41243.0</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>53373.12</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>53373.12</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>769.0390298511629</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>15888</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>15888.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>49.49</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>47.52</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>48.37</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>48.37</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>24243.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>56824.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>56824.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>41459.8</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>53916.64</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>53916.64</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>2889.582975043049</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>24243</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>24243.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>50.34</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>47.5</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>48.47</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>48.47</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>30520.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>68215.8</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>68215.8</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>40169.6</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>53954.14</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>53954.14</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>4920.553504779913</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>30520</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>30520.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>50.00000000000001</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>48.51</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>48.51</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>21044.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>65058.0</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>65058</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>38461.6</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>54408.58</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>54408.58</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>6973.670207804731</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>21044</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>21044.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>49.08</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>47.17</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>48.52</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>47.17</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>48.52</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>57221.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>62493.8</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>62493.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>37242.4</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>55416.48</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>55416.48</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>10672.92013327572</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>57221</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>57221.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>47.87</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>46.87</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>48.56</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>48.56</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>151095.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>52702.8</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>52702.8</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>32698.8</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>57013.98</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>57013.98</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>11700.28002204587</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>151095</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>151095.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>73.8</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>76.99</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>79.08</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>79.08</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>37918.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>22036.6</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>22036.6</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>25535.5</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>25490.96</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>25490.96</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-271.2655854032491</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>37918</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>37918.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>72.82000000000001</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>77.19</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>79.18</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>77.19</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>79.18000000000001</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>11598.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>18194.0</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>18194</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>23434.4</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>25778.86</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>25778.86</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-1805.975277406487</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>11598</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>11598.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>72.8</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>77.62</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>79.4</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>77.62</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>79.40000000000001</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>15841.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>21125.8</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>21125.8</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>23822.7</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>26161.88</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>26161.88</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-1113.918577503737</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>15841</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>15841.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>73.24000000000001</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>78.18</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>79.63</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>78.18000000000001</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>79.63</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>25532.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>23555.0</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>23555</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>24075.3</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>26666.0</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>26666</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-540.0904855889603</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>25532</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>25532.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>73.91999999999999</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>78.7</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>79.9</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>79.90000000000001</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>19294.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>25798.2</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>25798.2</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>24427.7</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>26711.82</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>26711.82</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-739.3685512253905</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>19294</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>74.5</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>79.12</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>80.11</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>80.11</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>18705.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>29034.4</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>29034.4</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>24219.8</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>26690.98</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>26690.98</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-329.2883395908102</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>18705</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>18705.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>75.8</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>79.54</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>80.36</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>80.36</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>26257.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>28674.8</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>28674.8</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>24972.0</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>27025.76</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>27025.76</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>331.4079748725417</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>26257</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>26257.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>76.74000000000001</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>79.88</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>80.6</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>79.88</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>80.59999999999999</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>27987.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>26519.6</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>26519.6</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>26046.7</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>26796.8</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>26796.8</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>454.280996431884</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>27987</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>27987.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>77.46</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>80.13</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>80.8</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>36748.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>24595.6</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>24595.6</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>25855.4</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>26803.94</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>26803.94</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>428.2324202155214</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>36748</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>36748.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>78.02000000000001</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>80.34</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>80.99</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>80.34</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>80.98999999999999</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>35475.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>23057.2</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>23057.2</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>23881.3</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>26874.84</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>26874.84</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-562.9524179584041</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>35475</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>35475.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>78.75999999999999</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>80.34</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>81.19</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>80.34</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>81.19</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>16907.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>19405.2</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>19405.2</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>23022.8</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>27026.78</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>27026.78</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-1822.432457565497</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>16907</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>16907.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
